--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-6.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9631ED34-3F70-42C2-A7FD-255CFC28AA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C57FA36-6DBE-436D-B11F-08194CA58595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{D3776A61-67DE-4BDE-9203-5ECC692C7919}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{92DE97C1-F586-4335-AF10-6544663289A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="175" r:id="rId3"/>
+    <pivotCache cacheId="207" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576912152777" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{C671AA80-71FA-40B8-809F-09D380F97E92}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579482986112" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{0F409454-E522-48DD-B136-F87705161D6C}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DB4D4A6E-5AFE-4DA7-A689-EAB544AA9A1A}" name="AllErrorPivot" cacheId="175" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EC8ED38-D360-48BD-82AD-7129CB012A93}" name="AllErrorPivot" cacheId="207" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -582,7 +582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256C6F58-25E6-41E8-8488-26905B8DBD7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E13542E-3655-449F-933D-2EE1FA68F571}">
   <dimension ref="A4:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -660,7 +660,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DD711-A608-4B32-AB03-2A47E8AEDFE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFA1794-B1B5-401B-A2FE-F528822D6FA7}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
